--- a/data/trans_camb/IP2004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 2,5</t>
+          <t>-8,85; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 4,72</t>
+          <t>-8,41; 5,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -2,81</t>
+          <t>-12,21; -2,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,78</t>
+          <t>-5,14; 8,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 2,48</t>
+          <t>-8,21; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 6,65</t>
+          <t>-6,79; 5,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,5</t>
+          <t>-5,26; 3,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 1,38</t>
+          <t>-7,01; 1,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 0,84</t>
+          <t>-7,8; 0,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 91,12</t>
+          <t>-80,5; 89,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,45; 131,9</t>
+          <t>-83,56; 130,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,16</t>
+          <t>-100,0; -13,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 267,0</t>
+          <t>-64,6; 285,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 151,7</t>
+          <t>-100,0; 124,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 291,21</t>
+          <t>-100,0; 216,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 85,46</t>
+          <t>-59,13; 77,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 29,92</t>
+          <t>-79,11; 31,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,77; 36,03</t>
+          <t>-89,79; 21,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,94</t>
+          <t>-2,03; 2,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,86</t>
+          <t>-1,95; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,04</t>
+          <t>-3,65; -0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,09</t>
+          <t>-3,42; 0,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,18</t>
+          <t>-3,73; -0,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,04</t>
+          <t>-3,76; -0,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,43</t>
+          <t>-2,12; 0,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,36</t>
+          <t>-2,24; 0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,54</t>
+          <t>-3,0; -0,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 96,14</t>
+          <t>-50,35; 90,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 87,86</t>
+          <t>-49,37; 91,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 8,82</t>
+          <t>-81,63; 7,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,67; 11,23</t>
+          <t>-71,04; 9,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 1,88</t>
+          <t>-77,7; -0,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 4,41</t>
+          <t>-74,85; 4,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,22; 15,41</t>
+          <t>-51,46; 18,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 13,94</t>
+          <t>-53,98; 17,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -17,61</t>
+          <t>-72,05; -17,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,84</t>
+          <t>-2,24; 3,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,38</t>
+          <t>-3,04; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,02</t>
+          <t>-3,82; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,75</t>
+          <t>1,07; 5,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,29</t>
+          <t>-0,8; 2,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,98</t>
+          <t>-1,54; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,28</t>
+          <t>-0,93; 2,31</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 577,36</t>
+          <t>-82,26; 523,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 439,36</t>
+          <t>-100,0; 360,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,79; 740,16</t>
+          <t>-65,21; 673,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-92,19; 350,28</t>
+          <t>-88,82; 362,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 712,78</t>
+          <t>-64,91; 651,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,34</t>
+          <t>-1,89; 1,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,97</t>
+          <t>-2,12; 1,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,99</t>
+          <t>-3,55; -0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,77</t>
+          <t>-2,18; 0,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,3</t>
+          <t>-2,82; -0,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,53</t>
+          <t>-2,36; 0,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,59</t>
+          <t>-1,67; 0,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,07</t>
+          <t>-2,09; -0,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; -0,5</t>
+          <t>-2,65; -0,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 50,94</t>
+          <t>-45,27; 48,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 36,35</t>
+          <t>-49,18; 42,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,34; -32,32</t>
+          <t>-83,47; -27,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 35,34</t>
+          <t>-56,56; 34,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,76; -10,32</t>
+          <t>-72,63; -5,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 23,8</t>
+          <t>-58,02; 25,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 25,13</t>
+          <t>-43,23; 18,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,54; -1,2</t>
+          <t>-55,22; -5,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,35; -16,39</t>
+          <t>-65,36; -18,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 3,27</t>
+          <t>-8,92; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 5,14</t>
+          <t>-8,46; 4,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -2,77</t>
+          <t>-13,66; -2,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 8,66</t>
+          <t>-4,87; 7,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 2,34</t>
+          <t>-8,34; 2,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 5,97</t>
+          <t>-7,21; 6,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,47</t>
+          <t>-5,08; 3,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 1,26</t>
+          <t>-6,91; 1,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 0,66</t>
+          <t>-8,42; 0,49</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 89,39</t>
+          <t>-81,35; 76,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 130,28</t>
+          <t>-83,22; 113,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,1</t>
+          <t>-100,0; 46,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 285,09</t>
+          <t>-60,34; 322,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,97</t>
+          <t>-98,44; 140,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 216,54</t>
+          <t>-100,0; 263,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 77,79</t>
+          <t>-58,95; 87,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,11; 31,09</t>
+          <t>-80,04; 38,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,79; 21,21</t>
+          <t>-90,87; 38,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,02</t>
+          <t>-2,02; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,99</t>
+          <t>-2,12; 1,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,11</t>
+          <t>-3,36; 0,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,18</t>
+          <t>-3,38; 0,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,17</t>
+          <t>-3,63; -0,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,04</t>
+          <t>-3,58; -0,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,47</t>
+          <t>-2,24; 0,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,42</t>
+          <t>-2,36; 0,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,57</t>
+          <t>-3,1; -0,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 90,82</t>
+          <t>-49,35; 98,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 91,91</t>
+          <t>-50,46; 95,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,63; 7,29</t>
+          <t>-80,23; 20,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,04; 9,83</t>
+          <t>-71,53; 11,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,7; -0,89</t>
+          <t>-76,98; -4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,85; 4,32</t>
+          <t>-76,58; 1,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 18,89</t>
+          <t>-53,25; 16,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 17,44</t>
+          <t>-56,05; 15,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,05; -17,59</t>
+          <t>-71,19; -14,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,69</t>
+          <t>-2,17; 3,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,43</t>
+          <t>-3,23; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,44</t>
+          <t>-4,22; 0,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,85</t>
+          <t>1,07; 5,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,31</t>
+          <t>-0,96; 2,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,07</t>
+          <t>-1,52; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,31</t>
+          <t>-0,79; 2,45</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,26; 523,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 360,88</t>
+          <t>-100,0; 500,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 673,41</t>
+          <t>-68,84; 601,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,82; 362,44</t>
+          <t>-88,73; 427,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 651,15</t>
+          <t>-64,04; 753,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,33</t>
+          <t>-1,83; 1,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,02</t>
+          <t>-2,33; 0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,89</t>
+          <t>-3,61; -0,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,85</t>
+          <t>-2,26; 0,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,17</t>
+          <t>-2,91; -0,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,61</t>
+          <t>-2,3; 0,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,53</t>
+          <t>-1,54; 0,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; -0,11</t>
+          <t>-2,09; -0,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,58</t>
+          <t>-2,55; -0,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 48,72</t>
+          <t>-43,62; 62,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 42,93</t>
+          <t>-52,41; 35,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,47; -27,58</t>
+          <t>-82,66; -27,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 34,04</t>
+          <t>-57,05; 36,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,63; -5,38</t>
+          <t>-72,53; -5,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 25,19</t>
+          <t>-58,28; 22,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 18,37</t>
+          <t>-40,54; 24,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-55,22; -5,01</t>
+          <t>-53,6; -1,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,36; -18,44</t>
+          <t>-66,41; -16,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,89</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,85</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-6,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 2,53</t>
+          <t>-5,3; 7,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,19</t>
+          <t>-8,5; 2,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; -2,93</t>
+          <t>-6,21; 7,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 7,91</t>
+          <t>-9,14; 2,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 2,44</t>
+          <t>-8,57; 4,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 6,17</t>
+          <t>-12,75; -2,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 3,7</t>
+          <t>-5,14; 3,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,36</t>
+          <t>-6,95; 1,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,49</t>
+          <t>-7,53; 1,67</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-49,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-10,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-37,85%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-33,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-90,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-49,52%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,24%</t>
+          <t>-90,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-57,99%</t>
+          <t>-52,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,35; 76,08</t>
+          <t>-71,14; 267,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,22; 113,44</t>
+          <t>-100,0; 151,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 46,84</t>
+          <t>-85,72; 342,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,34; 322,54</t>
+          <t>-80,52; 91,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-98,44; 140,63</t>
+          <t>-85,45; 131,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 263,81</t>
+          <t>-100,0; 35,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 87,76</t>
+          <t>-60,01; 85,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,04; 38,82</t>
+          <t>-82,21; 29,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,87; 38,24</t>
+          <t>-88,28; 47,94</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,83</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,9</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-1,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,99</t>
+          <t>-3,49; 0,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,94</t>
+          <t>-3,79; -0,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,19</t>
+          <t>-3,81; -0,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,17</t>
+          <t>-1,84; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; -0,24</t>
+          <t>-1,97; 1,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,07</t>
+          <t>-3,34; 0,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,44</t>
+          <t>-2,16; 0,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,35</t>
+          <t>-2,34; 0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; -0,56</t>
+          <t>-2,96; -0,49</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-41,41%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-49,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-51,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-1,65%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-0,61%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-53,84%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-41,41%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-49,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-49,15%</t>
+          <t>-48,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-51,22%</t>
+          <t>-50,19%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 98,62</t>
+          <t>-69,67; 11,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 95,9</t>
+          <t>-76,32; 1,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 20,33</t>
+          <t>-76,38; 1,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,53; 11,19</t>
+          <t>-47,5; 96,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,98; -4,75</t>
+          <t>-49,67; 87,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 1,43</t>
+          <t>-79,18; 23,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 16,55</t>
+          <t>-52,22; 15,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 15,05</t>
+          <t>-54,88; 13,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,19; -14,87</t>
+          <t>-71,17; -15,85</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,55</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,65</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,62</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,49</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,04</t>
+          <t>1,02; 5,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>-2,19; 3,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>-3,26; 1,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,84</t>
+          <t>-3,81; 0,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,24</t>
+          <t>-0,84; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,98</t>
+          <t>-1,58; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,45</t>
+          <t>-0,92; 2,23</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>32,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-34,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-75,14%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-72,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 500,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-78,95; 577,36</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 439,36</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 601,41</t>
+          <t>-66,79; 740,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,73; 427,31</t>
+          <t>-92,19; 350,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 753,86</t>
+          <t>-61,35; 716,05</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,52</t>
+          <t>-2,16; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,93</t>
+          <t>-2,89; -0,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -0,91</t>
+          <t>-2,38; 0,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,77</t>
+          <t>-1,85; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,29</t>
+          <t>-2,29; 0,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,51</t>
+          <t>-3,74; -0,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,67</t>
+          <t>-1,53; 0,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; -0,09</t>
+          <t>-2,24; -0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,55</t>
+          <t>-2,48; -0,47</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-22,99%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-48,46%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-28,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-7,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-17,67%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-65,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-22,99%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-48,46%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,99%</t>
+          <t>-62,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,52%</t>
+          <t>-45,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 62,47</t>
+          <t>-54,86; 35,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 35,3</t>
+          <t>-71,76; -10,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,66; -27,43</t>
+          <t>-58,82; 23,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,05; 36,49</t>
+          <t>-43,6; 50,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,53; -5,0</t>
+          <t>-51,94; 36,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 22,94</t>
+          <t>-82,97; -25,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 24,31</t>
+          <t>-40,14; 25,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,6; -1,43</t>
+          <t>-56,54; -1,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,41; -16,87</t>
+          <t>-63,86; -14,18</t>
         </is>
       </c>
     </row>
